--- a/artfynd/A 1370-2024 artfynd.xlsx
+++ b/artfynd/A 1370-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1370-2024 artfynd.xlsx
+++ b/artfynd/A 1370-2024 artfynd.xlsx
@@ -6447,10 +6447,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118536559</v>
+        <v>118537117</v>
       </c>
       <c r="B51" t="n">
-        <v>97846</v>
+        <v>91124</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6459,35 +6459,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6495,10 +6498,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>570086</v>
+        <v>570098</v>
       </c>
       <c r="R51" t="n">
-        <v>6425910</v>
+        <v>6425868</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6558,7 +6561,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118537298</v>
+        <v>118537657</v>
       </c>
       <c r="B52" t="n">
         <v>97846</v>
@@ -6597,11 +6600,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
@@ -6610,10 +6609,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>570140</v>
+        <v>570064</v>
       </c>
       <c r="R52" t="n">
-        <v>6425822</v>
+        <v>6425827</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6784,10 +6783,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118537137</v>
+        <v>118537145</v>
       </c>
       <c r="B54" t="n">
-        <v>97846</v>
+        <v>91124</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6796,39 +6795,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6836,10 +6834,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>570097</v>
+        <v>570115</v>
       </c>
       <c r="R54" t="n">
-        <v>6425875</v>
+        <v>6425880</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6899,10 +6897,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118537218</v>
+        <v>118537298</v>
       </c>
       <c r="B55" t="n">
-        <v>90524</v>
+        <v>97846</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6911,38 +6909,39 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6950,10 +6949,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>570157</v>
+        <v>570140</v>
       </c>
       <c r="R55" t="n">
-        <v>6425779</v>
+        <v>6425822</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7013,10 +7012,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118537608</v>
+        <v>118536442</v>
       </c>
       <c r="B56" t="n">
-        <v>90908</v>
+        <v>97846</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7025,49 +7024,50 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>A 1370, Hackenäs, Sm</t>
+          <t>A 1375, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>570083</v>
+        <v>570128</v>
       </c>
       <c r="R56" t="n">
-        <v>6425746</v>
+        <v>6425942</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7127,10 +7127,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118537557</v>
+        <v>118537218</v>
       </c>
       <c r="B57" t="n">
-        <v>91124</v>
+        <v>90524</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7139,49 +7139,49 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1339</v>
+        <v>5442</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>A 1375, Hackenäs, Sm</t>
+          <t>A 1370, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>570058</v>
+        <v>570157</v>
       </c>
       <c r="R57" t="n">
-        <v>6425703</v>
+        <v>6425779</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7241,10 +7241,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118537117</v>
+        <v>118537137</v>
       </c>
       <c r="B58" t="n">
-        <v>91124</v>
+        <v>97846</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7253,38 +7253,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7292,10 +7293,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>570098</v>
+        <v>570097</v>
       </c>
       <c r="R58" t="n">
-        <v>6425868</v>
+        <v>6425875</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7355,10 +7356,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118537712</v>
+        <v>118537557</v>
       </c>
       <c r="B59" t="n">
-        <v>90504</v>
+        <v>91124</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7367,25 +7368,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -7402,14 +7403,14 @@
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>A 1370, Hackenäs, Sm</t>
+          <t>A 1375, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>570064</v>
+        <v>570058</v>
       </c>
       <c r="R59" t="n">
-        <v>6425904</v>
+        <v>6425703</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7469,7 +7470,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118536442</v>
+        <v>118537682</v>
       </c>
       <c r="B60" t="n">
         <v>97846</v>
@@ -7517,14 +7518,14 @@
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>A 1375, Hackenäs, Sm</t>
+          <t>A 1370, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>570128</v>
+        <v>570039</v>
       </c>
       <c r="R60" t="n">
-        <v>6425942</v>
+        <v>6425893</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7809,10 +7810,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118537657</v>
+        <v>118537712</v>
       </c>
       <c r="B63" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7821,35 +7822,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7860,7 +7864,7 @@
         <v>570064</v>
       </c>
       <c r="R63" t="n">
-        <v>6425827</v>
+        <v>6425904</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7920,10 +7924,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118537682</v>
+        <v>118537608</v>
       </c>
       <c r="B64" t="n">
-        <v>97846</v>
+        <v>90908</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7932,39 +7936,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7972,10 +7975,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>570039</v>
+        <v>570083</v>
       </c>
       <c r="R64" t="n">
-        <v>6425893</v>
+        <v>6425746</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8035,10 +8038,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118537145</v>
+        <v>118536559</v>
       </c>
       <c r="B65" t="n">
-        <v>91124</v>
+        <v>97846</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8047,38 +8050,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>570115</v>
+        <v>570086</v>
       </c>
       <c r="R65" t="n">
-        <v>6425880</v>
+        <v>6425910</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 1370-2024 artfynd.xlsx
+++ b/artfynd/A 1370-2024 artfynd.xlsx
@@ -7127,10 +7127,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118537218</v>
+        <v>118537137</v>
       </c>
       <c r="B57" t="n">
-        <v>90524</v>
+        <v>97846</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7139,38 +7139,39 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7178,10 +7179,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>570157</v>
+        <v>570097</v>
       </c>
       <c r="R57" t="n">
-        <v>6425779</v>
+        <v>6425875</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7241,10 +7242,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118537137</v>
+        <v>118537218</v>
       </c>
       <c r="B58" t="n">
-        <v>97846</v>
+        <v>90524</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7253,39 +7254,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>570097</v>
+        <v>570157</v>
       </c>
       <c r="R58" t="n">
-        <v>6425875</v>
+        <v>6425779</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 1370-2024 artfynd.xlsx
+++ b/artfynd/A 1370-2024 artfynd.xlsx
@@ -6447,10 +6447,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118537117</v>
+        <v>118536527</v>
       </c>
       <c r="B51" t="n">
-        <v>91124</v>
+        <v>97846</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6459,38 +6459,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6498,10 +6495,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>570098</v>
+        <v>570119</v>
       </c>
       <c r="R51" t="n">
-        <v>6425868</v>
+        <v>6425945</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6561,10 +6558,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118537657</v>
+        <v>118537608</v>
       </c>
       <c r="B52" t="n">
-        <v>97846</v>
+        <v>90908</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6573,35 +6570,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6609,10 +6609,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>570064</v>
+        <v>570083</v>
       </c>
       <c r="R52" t="n">
-        <v>6425827</v>
+        <v>6425746</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6672,7 +6672,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118536527</v>
+        <v>118536559</v>
       </c>
       <c r="B53" t="n">
         <v>97846</v>
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>570119</v>
+        <v>570086</v>
       </c>
       <c r="R53" t="n">
-        <v>6425945</v>
+        <v>6425910</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6783,10 +6783,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118537145</v>
+        <v>118537712</v>
       </c>
       <c r="B54" t="n">
-        <v>91124</v>
+        <v>90504</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6795,25 +6795,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>570115</v>
+        <v>570064</v>
       </c>
       <c r="R54" t="n">
-        <v>6425880</v>
+        <v>6425904</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6897,7 +6897,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118537298</v>
+        <v>118537682</v>
       </c>
       <c r="B55" t="n">
         <v>97846</v>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>570140</v>
+        <v>570039</v>
       </c>
       <c r="R55" t="n">
-        <v>6425822</v>
+        <v>6425893</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7012,10 +7012,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118536442</v>
+        <v>118537167</v>
       </c>
       <c r="B56" t="n">
-        <v>97846</v>
+        <v>91124</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7024,50 +7024,49 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>A 1375, Hackenäs, Sm</t>
+          <t>A 1370, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>570128</v>
+        <v>570125</v>
       </c>
       <c r="R56" t="n">
-        <v>6425942</v>
+        <v>6425801</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7127,7 +7126,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118537137</v>
+        <v>118537298</v>
       </c>
       <c r="B57" t="n">
         <v>97846</v>
@@ -7179,10 +7178,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>570097</v>
+        <v>570140</v>
       </c>
       <c r="R57" t="n">
-        <v>6425875</v>
+        <v>6425822</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7242,10 +7241,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118537218</v>
+        <v>118537657</v>
       </c>
       <c r="B58" t="n">
-        <v>90524</v>
+        <v>97846</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7254,38 +7253,35 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7293,10 +7289,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>570157</v>
+        <v>570064</v>
       </c>
       <c r="R58" t="n">
-        <v>6425779</v>
+        <v>6425827</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7470,7 +7466,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118537682</v>
+        <v>118537137</v>
       </c>
       <c r="B60" t="n">
         <v>97846</v>
@@ -7522,10 +7518,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>570039</v>
+        <v>570097</v>
       </c>
       <c r="R60" t="n">
-        <v>6425893</v>
+        <v>6425875</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7696,10 +7692,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118537167</v>
+        <v>118537218</v>
       </c>
       <c r="B62" t="n">
-        <v>91124</v>
+        <v>90524</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7708,35 +7704,35 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1339</v>
+        <v>5442</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -7747,10 +7743,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>570125</v>
+        <v>570157</v>
       </c>
       <c r="R62" t="n">
-        <v>6425801</v>
+        <v>6425779</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7810,10 +7806,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118537712</v>
+        <v>118537145</v>
       </c>
       <c r="B63" t="n">
-        <v>90504</v>
+        <v>91124</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7822,25 +7818,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7861,10 +7857,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>570064</v>
+        <v>570115</v>
       </c>
       <c r="R63" t="n">
-        <v>6425904</v>
+        <v>6425880</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7924,10 +7920,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118537608</v>
+        <v>118537117</v>
       </c>
       <c r="B64" t="n">
-        <v>90908</v>
+        <v>91124</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7940,31 +7936,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5420</v>
+        <v>1339</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -7975,10 +7971,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>570083</v>
+        <v>570098</v>
       </c>
       <c r="R64" t="n">
-        <v>6425746</v>
+        <v>6425868</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8038,7 +8034,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118536559</v>
+        <v>118536442</v>
       </c>
       <c r="B65" t="n">
         <v>97846</v>
@@ -8077,19 +8073,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>A 1370, Hackenäs, Sm</t>
+          <t>A 1375, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>570086</v>
+        <v>570128</v>
       </c>
       <c r="R65" t="n">
-        <v>6425910</v>
+        <v>6425942</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 1370-2024 artfynd.xlsx
+++ b/artfynd/A 1370-2024 artfynd.xlsx
@@ -6339,7 +6339,7 @@
         <v>118485879</v>
       </c>
       <c r="B50" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6447,10 +6447,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118536527</v>
+        <v>118537712</v>
       </c>
       <c r="B51" t="n">
-        <v>97846</v>
+        <v>90511</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6459,35 +6459,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6495,10 +6498,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>570119</v>
+        <v>570064</v>
       </c>
       <c r="R51" t="n">
-        <v>6425945</v>
+        <v>6425904</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6558,10 +6561,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118537608</v>
+        <v>118536527</v>
       </c>
       <c r="B52" t="n">
-        <v>90908</v>
+        <v>97853</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6570,38 +6573,35 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6609,10 +6609,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>570083</v>
+        <v>570119</v>
       </c>
       <c r="R52" t="n">
-        <v>6425746</v>
+        <v>6425945</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6672,10 +6672,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118536559</v>
+        <v>118537137</v>
       </c>
       <c r="B53" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6711,7 +6711,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -6720,10 +6724,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>570086</v>
+        <v>570097</v>
       </c>
       <c r="R53" t="n">
-        <v>6425910</v>
+        <v>6425875</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6783,10 +6787,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118537712</v>
+        <v>118537608</v>
       </c>
       <c r="B54" t="n">
-        <v>90504</v>
+        <v>90915</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6795,35 +6799,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>5420</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -6834,10 +6838,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>570064</v>
+        <v>570083</v>
       </c>
       <c r="R54" t="n">
-        <v>6425904</v>
+        <v>6425746</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6897,10 +6901,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118537682</v>
+        <v>118536442</v>
       </c>
       <c r="B55" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6945,14 +6949,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>A 1370, Hackenäs, Sm</t>
+          <t>A 1375, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>570039</v>
+        <v>570128</v>
       </c>
       <c r="R55" t="n">
-        <v>6425893</v>
+        <v>6425942</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7012,10 +7016,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118537167</v>
+        <v>118537218</v>
       </c>
       <c r="B56" t="n">
-        <v>91124</v>
+        <v>90531</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7024,35 +7028,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1339</v>
+        <v>5442</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -7063,10 +7067,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>570125</v>
+        <v>570157</v>
       </c>
       <c r="R56" t="n">
-        <v>6425801</v>
+        <v>6425779</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7126,10 +7130,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118537298</v>
+        <v>118536559</v>
       </c>
       <c r="B57" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7165,11 +7169,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>570140</v>
+        <v>570086</v>
       </c>
       <c r="R57" t="n">
-        <v>6425822</v>
+        <v>6425910</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7241,10 +7241,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118537657</v>
+        <v>118537167</v>
       </c>
       <c r="B58" t="n">
-        <v>97846</v>
+        <v>91131</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7253,35 +7253,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7289,10 +7292,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>570064</v>
+        <v>570125</v>
       </c>
       <c r="R58" t="n">
-        <v>6425827</v>
+        <v>6425801</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7352,10 +7355,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118537557</v>
+        <v>118537117</v>
       </c>
       <c r="B59" t="n">
-        <v>91124</v>
+        <v>91131</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7399,14 +7402,14 @@
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>A 1375, Hackenäs, Sm</t>
+          <t>A 1370, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>570058</v>
+        <v>570098</v>
       </c>
       <c r="R59" t="n">
-        <v>6425703</v>
+        <v>6425868</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7466,10 +7469,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118537137</v>
+        <v>118537557</v>
       </c>
       <c r="B60" t="n">
-        <v>97846</v>
+        <v>91131</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7478,50 +7481,49 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>A 1370, Hackenäs, Sm</t>
+          <t>A 1375, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>570097</v>
+        <v>570058</v>
       </c>
       <c r="R60" t="n">
-        <v>6425875</v>
+        <v>6425703</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7581,10 +7583,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118537191</v>
+        <v>118537657</v>
       </c>
       <c r="B61" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7629,10 +7631,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>570140</v>
+        <v>570064</v>
       </c>
       <c r="R61" t="n">
-        <v>6425774</v>
+        <v>6425827</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7692,10 +7694,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118537218</v>
+        <v>118537682</v>
       </c>
       <c r="B62" t="n">
-        <v>90524</v>
+        <v>97853</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7704,38 +7706,39 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7743,10 +7746,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>570157</v>
+        <v>570039</v>
       </c>
       <c r="R62" t="n">
-        <v>6425779</v>
+        <v>6425893</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7806,10 +7809,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118537145</v>
+        <v>118537191</v>
       </c>
       <c r="B63" t="n">
-        <v>91124</v>
+        <v>97853</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7818,38 +7821,35 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7857,10 +7857,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>570115</v>
+        <v>570140</v>
       </c>
       <c r="R63" t="n">
-        <v>6425880</v>
+        <v>6425774</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7920,10 +7920,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118537117</v>
+        <v>118537298</v>
       </c>
       <c r="B64" t="n">
-        <v>91124</v>
+        <v>97853</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7932,38 +7932,39 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7971,10 +7972,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>570098</v>
+        <v>570140</v>
       </c>
       <c r="R64" t="n">
-        <v>6425868</v>
+        <v>6425822</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8034,10 +8035,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118536442</v>
+        <v>118537145</v>
       </c>
       <c r="B65" t="n">
-        <v>97846</v>
+        <v>91131</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8046,50 +8047,49 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>A 1375, Hackenäs, Sm</t>
+          <t>A 1370, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>570128</v>
+        <v>570115</v>
       </c>
       <c r="R65" t="n">
-        <v>6425942</v>
+        <v>6425880</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 1370-2024 artfynd.xlsx
+++ b/artfynd/A 1370-2024 artfynd.xlsx
@@ -6447,10 +6447,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118537712</v>
+        <v>118537557</v>
       </c>
       <c r="B51" t="n">
-        <v>90511</v>
+        <v>91131</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6459,25 +6459,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6494,14 +6494,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>A 1370, Hackenäs, Sm</t>
+          <t>A 1375, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>570064</v>
+        <v>570058</v>
       </c>
       <c r="R51" t="n">
-        <v>6425904</v>
+        <v>6425703</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6561,10 +6561,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118536527</v>
+        <v>118537167</v>
       </c>
       <c r="B52" t="n">
-        <v>97853</v>
+        <v>91131</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6573,35 +6573,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6609,10 +6612,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>570119</v>
+        <v>570125</v>
       </c>
       <c r="R52" t="n">
-        <v>6425945</v>
+        <v>6425801</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6672,10 +6675,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118537137</v>
+        <v>118537117</v>
       </c>
       <c r="B53" t="n">
-        <v>97853</v>
+        <v>91131</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6684,39 +6687,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6724,10 +6726,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>570097</v>
+        <v>570098</v>
       </c>
       <c r="R53" t="n">
-        <v>6425875</v>
+        <v>6425868</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6787,10 +6789,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118537608</v>
+        <v>118537298</v>
       </c>
       <c r="B54" t="n">
-        <v>90915</v>
+        <v>97853</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6799,38 +6801,39 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6838,10 +6841,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>570083</v>
+        <v>570140</v>
       </c>
       <c r="R54" t="n">
-        <v>6425746</v>
+        <v>6425822</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6901,10 +6904,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118536442</v>
+        <v>118537218</v>
       </c>
       <c r="B55" t="n">
-        <v>97853</v>
+        <v>90531</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6913,50 +6916,49 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>A 1375, Hackenäs, Sm</t>
+          <t>A 1370, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>570128</v>
+        <v>570157</v>
       </c>
       <c r="R55" t="n">
-        <v>6425942</v>
+        <v>6425779</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7016,10 +7018,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118537218</v>
+        <v>118537682</v>
       </c>
       <c r="B56" t="n">
-        <v>90531</v>
+        <v>97853</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7028,38 +7030,39 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7067,10 +7070,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>570157</v>
+        <v>570039</v>
       </c>
       <c r="R56" t="n">
-        <v>6425779</v>
+        <v>6425893</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7130,10 +7133,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118536559</v>
+        <v>118537145</v>
       </c>
       <c r="B57" t="n">
-        <v>97853</v>
+        <v>91131</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7142,35 +7145,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7178,10 +7184,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>570086</v>
+        <v>570115</v>
       </c>
       <c r="R57" t="n">
-        <v>6425910</v>
+        <v>6425880</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7241,10 +7247,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118537167</v>
+        <v>118537137</v>
       </c>
       <c r="B58" t="n">
-        <v>91131</v>
+        <v>97853</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7253,38 +7259,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7292,10 +7299,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>570125</v>
+        <v>570097</v>
       </c>
       <c r="R58" t="n">
-        <v>6425801</v>
+        <v>6425875</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7355,10 +7362,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118537117</v>
+        <v>118536559</v>
       </c>
       <c r="B59" t="n">
-        <v>91131</v>
+        <v>97853</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7367,38 +7374,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7406,10 +7410,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>570098</v>
+        <v>570086</v>
       </c>
       <c r="R59" t="n">
-        <v>6425868</v>
+        <v>6425910</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7469,10 +7473,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118537557</v>
+        <v>118536527</v>
       </c>
       <c r="B60" t="n">
-        <v>91131</v>
+        <v>97853</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7481,49 +7485,46 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>A 1375, Hackenäs, Sm</t>
+          <t>A 1370, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>570058</v>
+        <v>570119</v>
       </c>
       <c r="R60" t="n">
-        <v>6425703</v>
+        <v>6425945</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7694,10 +7695,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118537682</v>
+        <v>118537608</v>
       </c>
       <c r="B62" t="n">
-        <v>97853</v>
+        <v>90915</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7706,39 +7707,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>570039</v>
+        <v>570083</v>
       </c>
       <c r="R62" t="n">
-        <v>6425893</v>
+        <v>6425746</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7809,10 +7809,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118537191</v>
+        <v>118537712</v>
       </c>
       <c r="B63" t="n">
-        <v>97853</v>
+        <v>90511</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7821,35 +7821,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7857,10 +7860,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>570140</v>
+        <v>570064</v>
       </c>
       <c r="R63" t="n">
-        <v>6425774</v>
+        <v>6425904</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7920,7 +7923,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118537298</v>
+        <v>118536442</v>
       </c>
       <c r="B64" t="n">
         <v>97853</v>
@@ -7968,14 +7971,14 @@
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>A 1370, Hackenäs, Sm</t>
+          <t>A 1375, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>570140</v>
+        <v>570128</v>
       </c>
       <c r="R64" t="n">
-        <v>6425822</v>
+        <v>6425942</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8035,10 +8038,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118537145</v>
+        <v>118537191</v>
       </c>
       <c r="B65" t="n">
-        <v>91131</v>
+        <v>97853</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8047,38 +8050,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>570115</v>
+        <v>570140</v>
       </c>
       <c r="R65" t="n">
-        <v>6425880</v>
+        <v>6425774</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 1370-2024 artfynd.xlsx
+++ b/artfynd/A 1370-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>118537557</v>
       </c>
       <c r="B2" t="n">
-        <v>91133</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,6 +781,210 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>94849364</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Grundsjön-Hackenäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>570077</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6425714</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-07-10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-07-10</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114564246</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Haganäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>570073</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6425725</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-02-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-02-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
